--- a/InputData/geoeng/DACD/Direct Air Capture Data.xlsx
+++ b/InputData/geoeng/DACD/Direct Air Capture Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\geoeng\DACD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\geoeng\DACD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C171E834-3C4F-4014-A380-9FBA29E37E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EFFB3C-5D40-4B1A-8969-DEADFE8A46E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32625" yWindow="2040" windowWidth="24900" windowHeight="14490" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="106">
   <si>
     <t>Sources:</t>
   </si>
@@ -380,12 +381,6 @@
   </si>
   <si>
     <t>Heat Input Required per Ton CO2 Captured, Converted to Electricity</t>
-  </si>
-  <si>
-    <t>green hydrogen</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen</t>
   </si>
 </sst>
 </file>
@@ -948,28 +943,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" customWidth="1"/>
-    <col min="2" max="2" width="47.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="47.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -977,97 +972,97 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="6">
         <v>2021</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="6">
         <v>2019</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>76</v>
       </c>
@@ -1085,13 +1080,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C706B8D-FB10-40CA-B025-270C2E82347D}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.26953125" customWidth="1"/>
-    <col min="4" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="4" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>82</v>
       </c>
@@ -1099,7 +1094,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>95</v>
       </c>
@@ -1107,7 +1102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>96</v>
       </c>
@@ -1115,7 +1110,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>94</v>
       </c>
@@ -1123,7 +1118,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>97</v>
       </c>
@@ -1132,7 +1127,7 @@
         <v>8.9285714285714274E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -1141,37 +1136,37 @@
         <v>0.3571428571428571</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>2020</v>
       </c>
@@ -1185,7 +1180,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -1214,58 +1209,58 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H105"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.26953125" customWidth="1"/>
-    <col min="2" max="8" width="11.453125" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="8" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>73</v>
       </c>
@@ -1276,7 +1271,7 @@
       <c r="F12" s="14"/>
       <c r="G12" s="14"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1287,7 +1282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
@@ -1298,7 +1293,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>2</v>
       </c>
@@ -1309,7 +1304,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>3</v>
       </c>
@@ -1320,12 +1315,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -1336,7 +1331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
@@ -1347,7 +1342,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>2</v>
       </c>
@@ -1358,17 +1353,17 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
@@ -1379,7 +1374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>1</v>
       </c>
@@ -1390,7 +1385,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>2</v>
       </c>
@@ -1401,15 +1396,15 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
     </row>
-    <row r="30" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>103</v>
       </c>
@@ -1420,15 +1415,15 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
@@ -1439,7 +1434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>1</v>
       </c>
@@ -1452,7 +1447,7 @@
         <v>2.3759999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>2</v>
       </c>
@@ -1465,27 +1460,27 @@
         <v>1.452</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>43</v>
       </c>
@@ -1497,27 +1492,27 @@
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>2045</v>
       </c>
@@ -1540,7 +1535,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>29</v>
       </c>
@@ -1566,7 +1561,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>30</v>
       </c>
@@ -1592,7 +1587,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>31</v>
       </c>
@@ -1600,7 +1595,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>2045</v>
       </c>
@@ -1623,7 +1618,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>32</v>
       </c>
@@ -1656,7 +1651,7 @@
         <v>27.071428571428573</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>33</v>
       </c>
@@ -1689,27 +1684,27 @@
         <v>2.8571428571428568</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>38</v>
       </c>
@@ -1723,7 +1718,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -1737,7 +1732,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>42</v>
       </c>
@@ -1746,7 +1741,7 @@
         <v>0.24237500000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>44</v>
       </c>
@@ -1758,7 +1753,7 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B88">
         <v>2045</v>
       </c>
@@ -1781,7 +1776,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>32</v>
       </c>
@@ -1814,7 +1809,7 @@
         <v>6.5614375000000003</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>33</v>
       </c>
@@ -1847,12 +1842,12 @@
         <v>0.69249999999999989</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B93">
         <v>2045</v>
       </c>
@@ -1875,7 +1870,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>46</v>
       </c>
@@ -1908,7 +1903,7 @@
         <v>6561437500</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>47</v>
       </c>
@@ -1941,32 +1936,32 @@
         <v>692499999.99999988</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>54</v>
       </c>
@@ -1974,7 +1969,7 @@
         <v>947086</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>72</v>
       </c>
@@ -1992,16 +1987,16 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AI2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.81640625" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" customWidth="1"/>
-    <col min="3" max="24" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="35" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="24" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="35" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>48</v>
       </c>
@@ -2108,7 +2103,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -2259,14 +2254,14 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AI11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.7265625" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>55</v>
       </c>
@@ -2373,7 +2368,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -2514,7 +2509,7 @@
         <v>4236315.6780000003</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -2522,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="12">
-        <f t="shared" ref="C3:R13" si="1">$B3</f>
+        <f t="shared" ref="C3:R11" si="1">$B3</f>
         <v>0</v>
       </c>
       <c r="D3" s="12">
@@ -2654,7 +2649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -2794,7 +2789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -2934,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -3074,7 +3069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -3214,7 +3209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>65</v>
       </c>
@@ -3354,7 +3349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -3494,7 +3489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -3562,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="12">
-        <f t="shared" ref="D10:AI13" si="2">$B10</f>
+        <f t="shared" ref="D10:AI11" si="2">$B10</f>
         <v>0</v>
       </c>
       <c r="S10" s="12">
@@ -3634,7 +3629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -3770,286 +3765,6 @@
         <v>0</v>
       </c>
       <c r="AI11" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="X12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AE12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AF12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AG12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AI12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="X13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AD13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AE13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AF13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AG13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AI13" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4065,13 +3780,13 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AI2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.7265625" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -4178,7 +3893,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>57</v>
       </c>
